--- a/VerveStacks_JPN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E75C6FF-2A01-45AA-BC22-A61FA80200D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C03E044-9477-49BA-81B4-704ADDA9C9A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0E032F56-CF99-4AE6-A1C1-D40DCC5D882E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A9D59917-F0B5-4F39-99DE-56BD9DBF02CF}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -31,6 +31,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -68,1222 +71,1222 @@
     <t>ELC</t>
   </si>
   <si>
-    <t>e_JP1-275</t>
-  </si>
-  <si>
-    <t>e_JP3-275</t>
-  </si>
-  <si>
-    <t>g_JP1-275-JP3-275</t>
+    <t>e_JP1-275_JPN</t>
+  </si>
+  <si>
+    <t>e_JP3-275_JPN</t>
+  </si>
+  <si>
+    <t>g_JP1-275_JPN-JP3-275_JPN</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>e_JP10-500</t>
-  </si>
-  <si>
-    <t>e_w174636874-500</t>
-  </si>
-  <si>
-    <t>g_JP10-500-w174636874-500</t>
-  </si>
-  <si>
-    <t>e_JP100-500</t>
-  </si>
-  <si>
-    <t>e_JP103-500</t>
-  </si>
-  <si>
-    <t>g_JP100-500-JP103-500</t>
-  </si>
-  <si>
-    <t>e_JP101-500</t>
-  </si>
-  <si>
-    <t>g_JP101-500-JP100-500</t>
-  </si>
-  <si>
-    <t>e_JP102-500</t>
-  </si>
-  <si>
-    <t>e_JP96-500</t>
-  </si>
-  <si>
-    <t>g_JP102-500-JP96-500</t>
-  </si>
-  <si>
-    <t>e_JP111-500</t>
-  </si>
-  <si>
-    <t>g_JP103-500-JP111-500</t>
-  </si>
-  <si>
-    <t>e_JP106-500</t>
-  </si>
-  <si>
-    <t>g_JP106-500-JP102-500</t>
-  </si>
-  <si>
-    <t>e_JP112-500</t>
-  </si>
-  <si>
-    <t>g_JP106-500-JP112-500</t>
-  </si>
-  <si>
-    <t>e_JP107-500</t>
-  </si>
-  <si>
-    <t>e_JP110-500</t>
-  </si>
-  <si>
-    <t>g_JP107-500-JP110-500</t>
-  </si>
-  <si>
-    <t>e_JP108-500</t>
-  </si>
-  <si>
-    <t>g_JP108-500-JP107-500</t>
-  </si>
-  <si>
-    <t>e_JP109-500</t>
-  </si>
-  <si>
-    <t>g_JP109-500-JP108-500</t>
-  </si>
-  <si>
-    <t>g_JP109-500-JP111-500</t>
-  </si>
-  <si>
-    <t>g_JP111-500-JP109-500</t>
-  </si>
-  <si>
-    <t>g_JP112-500-JP106-500</t>
-  </si>
-  <si>
-    <t>e_JP116-500</t>
-  </si>
-  <si>
-    <t>e_w169031921-500</t>
-  </si>
-  <si>
-    <t>g_JP116-500-w169031921-500</t>
-  </si>
-  <si>
-    <t>e_w421647841-500</t>
-  </si>
-  <si>
-    <t>g_JP116-500-w421647841-500</t>
-  </si>
-  <si>
-    <t>e_JP117-500</t>
-  </si>
-  <si>
-    <t>e_w317511904-500</t>
-  </si>
-  <si>
-    <t>g_JP117-500-w317511904-500</t>
-  </si>
-  <si>
-    <t>e_JP118-500</t>
-  </si>
-  <si>
-    <t>g_JP118-500-w421647841-500</t>
-  </si>
-  <si>
-    <t>e_JP119-500</t>
-  </si>
-  <si>
-    <t>e_JP122-500</t>
-  </si>
-  <si>
-    <t>g_JP119-500-JP122-500</t>
-  </si>
-  <si>
-    <t>e_r11529219-500</t>
-  </si>
-  <si>
-    <t>g_JP119-500-r11529219-500</t>
-  </si>
-  <si>
-    <t>e_JP121-500</t>
-  </si>
-  <si>
-    <t>e_r11529637-500</t>
-  </si>
-  <si>
-    <t>g_JP121-500-r11529637-500</t>
-  </si>
-  <si>
-    <t>g_JP122-500-JP119-500</t>
-  </si>
-  <si>
-    <t>e_w170589736-500</t>
-  </si>
-  <si>
-    <t>g_JP122-500-w170589736-500</t>
-  </si>
-  <si>
-    <t>e_JP124-500</t>
-  </si>
-  <si>
-    <t>e_JP120-500</t>
-  </si>
-  <si>
-    <t>g_JP124-500-JP120-500</t>
-  </si>
-  <si>
-    <t>g_JP124-500-JP121-500</t>
-  </si>
-  <si>
-    <t>e_JP132-500</t>
-  </si>
-  <si>
-    <t>e_w315461259-500</t>
-  </si>
-  <si>
-    <t>g_JP132-500-w315461259-500</t>
-  </si>
-  <si>
-    <t>e_w315461272-500</t>
-  </si>
-  <si>
-    <t>g_JP132-500-w315461272-500</t>
-  </si>
-  <si>
-    <t>e_JP135-500</t>
-  </si>
-  <si>
-    <t>g_JP135-500-r11529637-500</t>
-  </si>
-  <si>
-    <t>e_JP141-500</t>
-  </si>
-  <si>
-    <t>e_w170568495-500</t>
-  </si>
-  <si>
-    <t>g_JP141-500-w170568495-500</t>
-  </si>
-  <si>
-    <t>e_JP156-500</t>
-  </si>
-  <si>
-    <t>g_JP156-500-JP141-500</t>
-  </si>
-  <si>
-    <t>g_JP156-500-w170589736-500</t>
-  </si>
-  <si>
-    <t>e_JP158-500</t>
-  </si>
-  <si>
-    <t>g_JP158-500-JP135-500</t>
-  </si>
-  <si>
-    <t>e_JP175-500</t>
-  </si>
-  <si>
-    <t>e_w241822631-500</t>
-  </si>
-  <si>
-    <t>g_JP175-500-w241822631-500</t>
-  </si>
-  <si>
-    <t>e_JP178-500</t>
-  </si>
-  <si>
-    <t>e_JP137-500</t>
-  </si>
-  <si>
-    <t>g_JP178-500-JP137-500</t>
-  </si>
-  <si>
-    <t>g_JP178-500-JP175-500</t>
-  </si>
-  <si>
-    <t>e_JP19-500</t>
-  </si>
-  <si>
-    <t>e_w659138214-500</t>
-  </si>
-  <si>
-    <t>g_JP19-500-w659138214-500</t>
-  </si>
-  <si>
-    <t>e_JP191-500</t>
-  </si>
-  <si>
-    <t>g_JP191-500-w170589736-500</t>
-  </si>
-  <si>
-    <t>e_JP2-275</t>
-  </si>
-  <si>
-    <t>e_JP5-275</t>
-  </si>
-  <si>
-    <t>g_JP2-275-JP5-275</t>
-  </si>
-  <si>
-    <t>e_JP21-500</t>
-  </si>
-  <si>
-    <t>e_JP36-500</t>
-  </si>
-  <si>
-    <t>g_JP21-500-JP36-500</t>
-  </si>
-  <si>
-    <t>e_JP218-500</t>
-  </si>
-  <si>
-    <t>e_w241822623-500</t>
-  </si>
-  <si>
-    <t>g_JP218-500-w241822623-500</t>
-  </si>
-  <si>
-    <t>e_JP219-500</t>
-  </si>
-  <si>
-    <t>e_w459476442-500</t>
-  </si>
-  <si>
-    <t>g_JP219-500-w459476442-500</t>
-  </si>
-  <si>
-    <t>e_JP23-500</t>
-  </si>
-  <si>
-    <t>e_w104391636-500</t>
-  </si>
-  <si>
-    <t>g_JP23-500-w104391636-500</t>
-  </si>
-  <si>
-    <t>e_JP248-500</t>
-  </si>
-  <si>
-    <t>e_w722673849-500</t>
-  </si>
-  <si>
-    <t>g_JP248-500-w722673849-500</t>
-  </si>
-  <si>
-    <t>e_JP249-500</t>
-  </si>
-  <si>
-    <t>e_w1037516198-500</t>
-  </si>
-  <si>
-    <t>g_JP249-500-w1037516198-500</t>
-  </si>
-  <si>
-    <t>e_JP267-500</t>
-  </si>
-  <si>
-    <t>e_w172601929-500</t>
-  </si>
-  <si>
-    <t>g_JP267-500-w172601929-500</t>
-  </si>
-  <si>
-    <t>e_w185029969-500</t>
-  </si>
-  <si>
-    <t>g_JP267-500-w185029969-500</t>
-  </si>
-  <si>
-    <t>e_JP269-500</t>
-  </si>
-  <si>
-    <t>g_JP269-500-w185029969-500</t>
-  </si>
-  <si>
-    <t>e_JP28-500</t>
-  </si>
-  <si>
-    <t>g_JP28-500-JP21-500</t>
-  </si>
-  <si>
-    <t>e_JP29-500</t>
-  </si>
-  <si>
-    <t>e_JP37-500</t>
-  </si>
-  <si>
-    <t>g_JP29-500-JP37-500</t>
-  </si>
-  <si>
-    <t>e_JP292-500</t>
-  </si>
-  <si>
-    <t>e_JP294-500</t>
-  </si>
-  <si>
-    <t>g_JP292-500-JP294-500</t>
-  </si>
-  <si>
-    <t>e_w216502300-500</t>
-  </si>
-  <si>
-    <t>g_JP294-500-w216502300-500</t>
-  </si>
-  <si>
-    <t>e_JP296-500</t>
-  </si>
-  <si>
-    <t>e_w216778426-500</t>
-  </si>
-  <si>
-    <t>g_JP296-500-w216778426-500</t>
-  </si>
-  <si>
-    <t>e_JP30-500</t>
-  </si>
-  <si>
-    <t>g_JP30-500-JP29-500</t>
-  </si>
-  <si>
-    <t>e_JP306-500</t>
-  </si>
-  <si>
-    <t>e_w215451416-500</t>
-  </si>
-  <si>
-    <t>g_JP306-500-w215451416-500</t>
-  </si>
-  <si>
-    <t>e_JP34-500</t>
-  </si>
-  <si>
-    <t>g_JP34-500-JP36-500</t>
-  </si>
-  <si>
-    <t>e_w66098469-500</t>
-  </si>
-  <si>
-    <t>g_JP36-500-w66098469-500</t>
-  </si>
-  <si>
-    <t>e_JP41-500</t>
-  </si>
-  <si>
-    <t>g_JP37-500-JP41-500</t>
-  </si>
-  <si>
-    <t>e_JP4-275</t>
-  </si>
-  <si>
-    <t>g_JP4-275-JP2-275</t>
-  </si>
-  <si>
-    <t>g_JP4-275-JP5-275</t>
-  </si>
-  <si>
-    <t>e_w168857610-500</t>
-  </si>
-  <si>
-    <t>g_JP41-500-w168857610-500</t>
-  </si>
-  <si>
-    <t>e_JP49-500</t>
-  </si>
-  <si>
-    <t>e_JP50-500</t>
-  </si>
-  <si>
-    <t>g_JP49-500-JP50-500</t>
-  </si>
-  <si>
-    <t>g_JP5-275-JP2-275</t>
-  </si>
-  <si>
-    <t>e_JP6-275</t>
-  </si>
-  <si>
-    <t>g_JP5-275-JP6-275</t>
-  </si>
-  <si>
-    <t>e_w801582512-275</t>
-  </si>
-  <si>
-    <t>g_JP5-275-w801582512-275</t>
-  </si>
-  <si>
-    <t>e_w133641619-500</t>
-  </si>
-  <si>
-    <t>g_JP50-500-w133641619-500</t>
-  </si>
-  <si>
-    <t>e_JP57-500</t>
-  </si>
-  <si>
-    <t>e_w169249243-500</t>
-  </si>
-  <si>
-    <t>g_JP57-500-w169249243-500</t>
-  </si>
-  <si>
-    <t>g_JP6-275-JP5-275</t>
-  </si>
-  <si>
-    <t>e_JP7-275</t>
-  </si>
-  <si>
-    <t>g_JP6-275-JP7-275</t>
-  </si>
-  <si>
-    <t>e_JP60-500</t>
-  </si>
-  <si>
-    <t>e_w104530060-500</t>
-  </si>
-  <si>
-    <t>g_JP60-500-w104530060-500</t>
-  </si>
-  <si>
-    <t>g_JP7-275-JP6-275</t>
-  </si>
-  <si>
-    <t>e_JP74-500</t>
-  </si>
-  <si>
-    <t>g_JP74-500-JP57-500</t>
-  </si>
-  <si>
-    <t>e_JP76-500</t>
-  </si>
-  <si>
-    <t>e_JP73-500</t>
-  </si>
-  <si>
-    <t>g_JP76-500-JP73-500</t>
-  </si>
-  <si>
-    <t>e_JP9-500</t>
-  </si>
-  <si>
-    <t>e_w1028554758-500</t>
-  </si>
-  <si>
-    <t>g_JP9-500-w1028554758-500</t>
-  </si>
-  <si>
-    <t>e_JP95-500</t>
-  </si>
-  <si>
-    <t>e_w150035494-500</t>
-  </si>
-  <si>
-    <t>g_JP95-500-w150035494-500</t>
-  </si>
-  <si>
-    <t>e_w832823487-500</t>
-  </si>
-  <si>
-    <t>g_JP96-500-w832823487-500</t>
-  </si>
-  <si>
-    <t>g_r11529219-500-JP118-500</t>
-  </si>
-  <si>
-    <t>g_r11529637-500-JP124-500</t>
-  </si>
-  <si>
-    <t>e_JP155-500</t>
-  </si>
-  <si>
-    <t>g_r11529637-500-JP155-500</t>
-  </si>
-  <si>
-    <t>e_r13768299-500</t>
-  </si>
-  <si>
-    <t>e_w168727982-500</t>
-  </si>
-  <si>
-    <t>g_r13768299-500-w168727982-500</t>
-  </si>
-  <si>
-    <t>e_r15580570-500</t>
-  </si>
-  <si>
-    <t>g_r15580570-500-r13768299-500</t>
-  </si>
-  <si>
-    <t>e_w132913106-500</t>
-  </si>
-  <si>
-    <t>g_r15580570-500-w132913106-500</t>
-  </si>
-  <si>
-    <t>e_w168839127-500</t>
-  </si>
-  <si>
-    <t>g_r15580570-500-w168839127-500</t>
-  </si>
-  <si>
-    <t>e_r17013811-500</t>
-  </si>
-  <si>
-    <t>e_JP25-500</t>
-  </si>
-  <si>
-    <t>g_r17013811-500-JP25-500</t>
-  </si>
-  <si>
-    <t>g_r17013811-500-w169249243-500</t>
-  </si>
-  <si>
-    <t>e_w256682313-500</t>
-  </si>
-  <si>
-    <t>g_r17013811-500-w256682313-500</t>
-  </si>
-  <si>
-    <t>e_r2269992-500</t>
-  </si>
-  <si>
-    <t>g_r2269992-500-JP110-500</t>
-  </si>
-  <si>
-    <t>e_w714627759-500</t>
-  </si>
-  <si>
-    <t>g_w1028554758-500-w714627759-500</t>
-  </si>
-  <si>
-    <t>e_w1029010255-500</t>
-  </si>
-  <si>
-    <t>g_w1029010255-500-r11529219-500</t>
-  </si>
-  <si>
-    <t>e_w102958903-500</t>
-  </si>
-  <si>
-    <t>e_w87538349-500</t>
-  </si>
-  <si>
-    <t>g_w102958903-500-w87538349-500</t>
-  </si>
-  <si>
-    <t>e_w1030329139-500</t>
-  </si>
-  <si>
-    <t>g_w1030329139-500-JP29-500</t>
-  </si>
-  <si>
-    <t>e_w106309481-500</t>
-  </si>
-  <si>
-    <t>g_w104391636-500-w106309481-500</t>
-  </si>
-  <si>
-    <t>g_w104391636-500-w132913106-500</t>
-  </si>
-  <si>
-    <t>g_w104391636-500-w168839127-500</t>
-  </si>
-  <si>
-    <t>g_w104530060-500-w168839127-500</t>
-  </si>
-  <si>
-    <t>e_w104173570-500</t>
-  </si>
-  <si>
-    <t>g_w106309481-500-w104173570-500</t>
-  </si>
-  <si>
-    <t>e_w109834508-500</t>
-  </si>
-  <si>
-    <t>e_w109850439-500</t>
-  </si>
-  <si>
-    <t>g_w109834508-500-w109850439-500</t>
-  </si>
-  <si>
-    <t>e_w169031998-500</t>
-  </si>
-  <si>
-    <t>g_w109850439-500-w169031998-500</t>
-  </si>
-  <si>
-    <t>e_w291678103-500</t>
-  </si>
-  <si>
-    <t>g_w109850439-500-w291678103-500</t>
-  </si>
-  <si>
-    <t>e_w110682956-500</t>
-  </si>
-  <si>
-    <t>g_w110682956-500-JP158-500</t>
-  </si>
-  <si>
-    <t>e_w105298089-500</t>
-  </si>
-  <si>
-    <t>g_w132913106-500-w105298089-500</t>
-  </si>
-  <si>
-    <t>g_w133641619-500-r15580570-500</t>
-  </si>
-  <si>
-    <t>e_w128581912-500</t>
-  </si>
-  <si>
-    <t>g_w133641619-500-w128581912-500</t>
-  </si>
-  <si>
-    <t>e_w133644487-500</t>
-  </si>
-  <si>
-    <t>g_w133641619-500-w133644487-500</t>
-  </si>
-  <si>
-    <t>e_w145079972-500</t>
-  </si>
-  <si>
-    <t>g_w133644487-500-w145079972-500</t>
-  </si>
-  <si>
-    <t>e_w142662111-500</t>
-  </si>
-  <si>
-    <t>e_w116559939-500</t>
-  </si>
-  <si>
-    <t>g_w142662111-500-w116559939-500</t>
-  </si>
-  <si>
-    <t>e_w170850727-500</t>
-  </si>
-  <si>
-    <t>g_w142662111-500-w170850727-500</t>
-  </si>
-  <si>
-    <t>e_w209429410-500</t>
-  </si>
-  <si>
-    <t>g_w142662111-500-w209429410-500</t>
-  </si>
-  <si>
-    <t>g_w142662111-500-w459476442-500</t>
-  </si>
-  <si>
-    <t>e_w149843487-500</t>
-  </si>
-  <si>
-    <t>g_w145079972-500-w149843487-500</t>
-  </si>
-  <si>
-    <t>e_w150065045-500</t>
-  </si>
-  <si>
-    <t>g_w150035494-500-w150065045-500</t>
-  </si>
-  <si>
-    <t>g_w150065045-500-w149843487-500</t>
-  </si>
-  <si>
-    <t>e_w151379730-500</t>
-  </si>
-  <si>
-    <t>g_w151379730-500-w168727982-500</t>
-  </si>
-  <si>
-    <t>e_w156208858-500</t>
-  </si>
-  <si>
-    <t>g_w156208858-500-JP19-500</t>
-  </si>
-  <si>
-    <t>e_w253566674-500</t>
-  </si>
-  <si>
-    <t>g_w156208858-500-w253566674-500</t>
-  </si>
-  <si>
-    <t>e_w161727149-500</t>
-  </si>
-  <si>
-    <t>g_w161727149-500-JP191-500</t>
-  </si>
-  <si>
-    <t>e_w161870227-500</t>
-  </si>
-  <si>
-    <t>g_w161727149-500-w161870227-500</t>
-  </si>
-  <si>
-    <t>e_w169359724-500</t>
-  </si>
-  <si>
-    <t>g_w161727149-500-w169359724-500</t>
-  </si>
-  <si>
-    <t>g_w161870227-500-w169031998-500</t>
-  </si>
-  <si>
-    <t>g_w161870227-500-w170589736-500</t>
-  </si>
-  <si>
-    <t>g_w168727982-500-JP101-500</t>
-  </si>
-  <si>
-    <t>g_w168727982-500-w105298089-500</t>
-  </si>
-  <si>
-    <t>g_w168857610-500-w104391636-500</t>
-  </si>
-  <si>
-    <t>g_w168857610-500-w104530060-500</t>
-  </si>
-  <si>
-    <t>g_w169031921-500-w161727149-500</t>
-  </si>
-  <si>
-    <t>e_w320438391-500</t>
-  </si>
-  <si>
-    <t>g_w169031921-500-w320438391-500</t>
-  </si>
-  <si>
-    <t>g_w169031921-500-w421647841-500</t>
-  </si>
-  <si>
-    <t>e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>g_w169031998-500-w1038584990-500</t>
-  </si>
-  <si>
-    <t>e_w169122898-500</t>
-  </si>
-  <si>
-    <t>g_w169122898-500-w116559939-500</t>
-  </si>
-  <si>
-    <t>e_w161946849-500</t>
-  </si>
-  <si>
-    <t>g_w169122898-500-w161946849-500</t>
-  </si>
-  <si>
-    <t>g_w169359724-500-JP249-500</t>
-  </si>
-  <si>
-    <t>g_w169359724-500-w109834508-500</t>
-  </si>
-  <si>
-    <t>e_w169963227-500</t>
-  </si>
-  <si>
-    <t>e_w195615141-500</t>
-  </si>
-  <si>
-    <t>g_w169963227-500-w195615141-500</t>
-  </si>
-  <si>
-    <t>g_w169963227-500-w66098469-500</t>
-  </si>
-  <si>
-    <t>e_w170247312-500</t>
-  </si>
-  <si>
-    <t>g_w170247312-500-w169122898-500</t>
-  </si>
-  <si>
-    <t>e_w170366035-500</t>
-  </si>
-  <si>
-    <t>g_w170366035-500-w161946849-500</t>
-  </si>
-  <si>
-    <t>g_w170366035-500-w170850727-500</t>
-  </si>
-  <si>
-    <t>e_w975217734-500</t>
-  </si>
-  <si>
-    <t>g_w170366035-500-w975217734-500</t>
-  </si>
-  <si>
-    <t>e_w170537514-500</t>
-  </si>
-  <si>
-    <t>e_w190769051-500</t>
-  </si>
-  <si>
-    <t>g_w170537514-500-w190769051-500</t>
-  </si>
-  <si>
-    <t>g_w170568495-500-w170366035-500</t>
-  </si>
-  <si>
-    <t>g_w170568495-500-w170537514-500</t>
-  </si>
-  <si>
-    <t>e_w170605907-500</t>
-  </si>
-  <si>
-    <t>g_w170605907-500-JP178-500</t>
-  </si>
-  <si>
-    <t>g_w170605907-500-w110682956-500</t>
-  </si>
-  <si>
-    <t>e_w171066843-500</t>
-  </si>
-  <si>
-    <t>g_w171066843-500-w87538349-500</t>
-  </si>
-  <si>
-    <t>e_w172144358-500</t>
-  </si>
-  <si>
-    <t>g_w172144358-500-w172601929-500</t>
-  </si>
-  <si>
-    <t>e_w201293312-500</t>
-  </si>
-  <si>
-    <t>g_w172144358-500-w201293312-500</t>
-  </si>
-  <si>
-    <t>e_w405626236-500</t>
-  </si>
-  <si>
-    <t>g_w172144358-500-w405626236-500</t>
-  </si>
-  <si>
-    <t>e_w187988970-500</t>
-  </si>
-  <si>
-    <t>g_w172601929-500-w187988970-500</t>
-  </si>
-  <si>
-    <t>e_w172907196-500</t>
-  </si>
-  <si>
-    <t>e_w1037299172-500</t>
-  </si>
-  <si>
-    <t>g_w172907196-500-w1037299172-500</t>
-  </si>
-  <si>
-    <t>g_w172907196-500-w171066843-500</t>
-  </si>
-  <si>
-    <t>e_w106076988-500</t>
-  </si>
-  <si>
-    <t>g_w174636874-500-w106076988-500</t>
-  </si>
-  <si>
-    <t>e_w179863079-275</t>
-  </si>
-  <si>
-    <t>g_w179863079-275-JP2-275</t>
-  </si>
-  <si>
-    <t>g_w179863079-275-JP6-275</t>
-  </si>
-  <si>
-    <t>g_w185029969-500-w172144358-500</t>
-  </si>
-  <si>
-    <t>e_w186510275-500</t>
-  </si>
-  <si>
-    <t>g_w186510275-500-JP267-500</t>
-  </si>
-  <si>
-    <t>g_w187988970-500-w201293312-500</t>
-  </si>
-  <si>
-    <t>e_w204258596-500</t>
-  </si>
-  <si>
-    <t>g_w187988970-500-w204258596-500</t>
-  </si>
-  <si>
-    <t>g_w190769051-500-JP112-500</t>
-  </si>
-  <si>
-    <t>g_w190769051-500-w161946849-500</t>
-  </si>
-  <si>
-    <t>e_w193544791-500</t>
-  </si>
-  <si>
-    <t>e_w170974371-500</t>
-  </si>
-  <si>
-    <t>g_w193544791-500-w170974371-500</t>
-  </si>
-  <si>
-    <t>e_w317416612-500</t>
-  </si>
-  <si>
-    <t>g_w193544791-500-w317416612-500</t>
-  </si>
-  <si>
-    <t>g_w195615141-500-w145079972-500</t>
-  </si>
-  <si>
-    <t>g_w201293312-500-w216778426-500</t>
-  </si>
-  <si>
-    <t>g_w204258596-500-w317416612-500</t>
-  </si>
-  <si>
-    <t>e_w209726348-500</t>
-  </si>
-  <si>
-    <t>g_w209429410-500-w209726348-500</t>
-  </si>
-  <si>
-    <t>e_w210090094-500</t>
-  </si>
-  <si>
-    <t>g_w210090094-500-JP219-500</t>
-  </si>
-  <si>
-    <t>g_w210090094-500-w116559939-500</t>
-  </si>
-  <si>
-    <t>e_w211412000-500</t>
-  </si>
-  <si>
-    <t>g_w211412000-500-w315461272-500</t>
-  </si>
-  <si>
-    <t>e_w216956620-500</t>
-  </si>
-  <si>
-    <t>g_w215451416-500-w216956620-500</t>
-  </si>
-  <si>
-    <t>g_w216502300-500-w215451416-500</t>
-  </si>
-  <si>
-    <t>g_w216502300-500-w405626236-500</t>
-  </si>
-  <si>
-    <t>e_w216953915-500</t>
-  </si>
-  <si>
-    <t>g_w216956620-500-w216953915-500</t>
-  </si>
-  <si>
-    <t>e_w241822621-500</t>
-  </si>
-  <si>
-    <t>g_w241822621-500-JP155-500</t>
-  </si>
-  <si>
-    <t>g_w241822621-500-w320438391-500</t>
-  </si>
-  <si>
-    <t>g_w241822623-500-w241822631-500</t>
-  </si>
-  <si>
-    <t>g_w241822631-500-w241822621-500</t>
-  </si>
-  <si>
-    <t>e_w241828221-500</t>
-  </si>
-  <si>
-    <t>g_w241828221-500-w170974371-500</t>
-  </si>
-  <si>
-    <t>g_w241828221-500-w241822623-500</t>
-  </si>
-  <si>
-    <t>e_w242103481-500</t>
-  </si>
-  <si>
-    <t>g_w241828221-500-w242103481-500</t>
-  </si>
-  <si>
-    <t>e_w242253537-500</t>
-  </si>
-  <si>
-    <t>g_w242103481-500-w242253537-500</t>
-  </si>
-  <si>
-    <t>e_w242103532-500</t>
-  </si>
-  <si>
-    <t>g_w242103532-500-JP218-500</t>
-  </si>
-  <si>
-    <t>g_w242103532-500-w102958903-500</t>
-  </si>
-  <si>
-    <t>e_w242253500-500</t>
-  </si>
-  <si>
-    <t>g_w242253500-500-w193544791-500</t>
-  </si>
-  <si>
-    <t>g_w242253500-500-w204258596-500</t>
-  </si>
-  <si>
-    <t>g_w242253537-500-w241822621-500</t>
-  </si>
-  <si>
-    <t>e_w250540807-500</t>
-  </si>
-  <si>
-    <t>e_w505170104-500</t>
-  </si>
-  <si>
-    <t>g_w250540807-500-w505170104-500</t>
-  </si>
-  <si>
-    <t>e_w253566674-1000</t>
-  </si>
-  <si>
-    <t>e_w250540807-1000</t>
-  </si>
-  <si>
-    <t>g_w253566674-1000-w250540807-1000</t>
-  </si>
-  <si>
-    <t>g_w253566674-500-w104391636-500</t>
-  </si>
-  <si>
-    <t>g_w256682313-500-w169249243-500</t>
-  </si>
-  <si>
-    <t>g_w291678103-500-w109834508-500</t>
-  </si>
-  <si>
-    <t>e_w307942220-500</t>
-  </si>
-  <si>
-    <t>g_w307942220-500-w722673849-500</t>
-  </si>
-  <si>
-    <t>e_w315434358-500</t>
-  </si>
-  <si>
-    <t>g_w315434358-500-w195615141-500</t>
-  </si>
-  <si>
-    <t>g_w315461272-500-w105298089-500</t>
-  </si>
-  <si>
-    <t>e_w315618377-500</t>
-  </si>
-  <si>
-    <t>g_w315618377-500-r11529219-500</t>
-  </si>
-  <si>
-    <t>g_w315618377-500-w256682313-500</t>
-  </si>
-  <si>
-    <t>e_w315662839-500</t>
-  </si>
-  <si>
-    <t>g_w315662839-500-w195615141-500</t>
-  </si>
-  <si>
-    <t>g_w317416612-500-w242103481-500</t>
-  </si>
-  <si>
-    <t>g_w317511904-500-w242103481-500</t>
-  </si>
-  <si>
-    <t>g_w320438391-500-r11529637-500</t>
-  </si>
-  <si>
-    <t>g_w421647841-500-JP118-500</t>
-  </si>
-  <si>
-    <t>g_w421647841-500-w110682956-500</t>
-  </si>
-  <si>
-    <t>g_w421647841-500-w161870227-500</t>
-  </si>
-  <si>
-    <t>g_w459476442-500-w210090094-500</t>
-  </si>
-  <si>
-    <t>g_w505170104-500-JP60-500</t>
-  </si>
-  <si>
-    <t>g_w505170104-500-w128581912-500</t>
-  </si>
-  <si>
-    <t>g_w505170104-500-w315434358-500</t>
-  </si>
-  <si>
-    <t>e_w785319805-500</t>
-  </si>
-  <si>
-    <t>g_w659138214-500-w785319805-500</t>
-  </si>
-  <si>
-    <t>e_w66098469-1000</t>
-  </si>
-  <si>
-    <t>e_JP28-1000</t>
-  </si>
-  <si>
-    <t>g_w66098469-1000-JP28-1000</t>
-  </si>
-  <si>
-    <t>e_w150035494-1000</t>
-  </si>
-  <si>
-    <t>g_w66098469-1000-w150035494-1000</t>
-  </si>
-  <si>
-    <t>g_w66098469-1000-w250540807-1000</t>
-  </si>
-  <si>
-    <t>g_w66098469-500-JP49-500</t>
-  </si>
-  <si>
-    <t>g_w714627759-500-JP10-500</t>
-  </si>
-  <si>
-    <t>g_w785319805-500-w106076988-500</t>
-  </si>
-  <si>
-    <t>g_w801582512-275-JP5-275</t>
-  </si>
-  <si>
-    <t>e_JP8-275</t>
-  </si>
-  <si>
-    <t>g_w801582512-275-JP8-275</t>
-  </si>
-  <si>
-    <t>g_w87538349-500-w307942220-500</t>
-  </si>
-  <si>
-    <t>e_w901872439-500</t>
-  </si>
-  <si>
-    <t>g_w901872439-500-JP19-500</t>
-  </si>
-  <si>
-    <t>e_w901872431-500</t>
-  </si>
-  <si>
-    <t>g_w901872439-500-w901872431-500</t>
-  </si>
-  <si>
-    <t>g_w975217734-500-JP74-500</t>
+    <t>e_JP10-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w174636874-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP10-500_JPN-w174636874-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP100-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP103-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP100-500_JPN-JP103-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP101-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP101-500_JPN-JP100-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP102-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP96-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP102-500_JPN-JP96-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP111-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP103-500_JPN-JP111-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP106-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP106-500_JPN-JP102-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP112-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP106-500_JPN-JP112-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP107-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP110-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP107-500_JPN-JP110-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP108-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP108-500_JPN-JP107-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP109-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP109-500_JPN-JP108-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP109-500_JPN-JP111-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP111-500_JPN-JP109-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP112-500_JPN-JP106-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP116-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w169031921-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP116-500_JPN-w169031921-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w421647841-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP116-500_JPN-w421647841-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP117-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w317511904-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP117-500_JPN-w317511904-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP118-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP118-500_JPN-w421647841-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP119-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP122-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP119-500_JPN-JP122-500_JPN</t>
+  </si>
+  <si>
+    <t>e_r11529219-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP119-500_JPN-r11529219-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP121-500_JPN</t>
+  </si>
+  <si>
+    <t>e_r11529637-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP121-500_JPN-r11529637-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP122-500_JPN-JP119-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w170589736-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP122-500_JPN-w170589736-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP124-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP120-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP124-500_JPN-JP120-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP124-500_JPN-JP121-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP132-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w315461259-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP132-500_JPN-w315461259-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w315461272-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP132-500_JPN-w315461272-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP135-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP135-500_JPN-r11529637-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP141-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w170568495-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP141-500_JPN-w170568495-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP156-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP156-500_JPN-JP141-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP156-500_JPN-w170589736-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP158-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP158-500_JPN-JP135-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP175-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w241822631-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP175-500_JPN-w241822631-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP178-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP137-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP178-500_JPN-JP137-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP178-500_JPN-JP175-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP19-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w659138214-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP19-500_JPN-w659138214-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP191-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP191-500_JPN-w170589736-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP2-275_JPN</t>
+  </si>
+  <si>
+    <t>e_JP5-275_JPN</t>
+  </si>
+  <si>
+    <t>g_JP2-275_JPN-JP5-275_JPN</t>
+  </si>
+  <si>
+    <t>e_JP21-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP36-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP21-500_JPN-JP36-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP218-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w241822623-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP218-500_JPN-w241822623-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP219-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w459476442-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP219-500_JPN-w459476442-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP23-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w104391636-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP23-500_JPN-w104391636-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP248-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w722673849-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP248-500_JPN-w722673849-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP249-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w1037516198-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP249-500_JPN-w1037516198-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP267-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w172601929-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP267-500_JPN-w172601929-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w185029969-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP267-500_JPN-w185029969-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP269-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP269-500_JPN-w185029969-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP28-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP28-500_JPN-JP21-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP29-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP37-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP29-500_JPN-JP37-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP292-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP294-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP292-500_JPN-JP294-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w216502300-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP294-500_JPN-w216502300-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP296-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w216778426-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP296-500_JPN-w216778426-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP30-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP30-500_JPN-JP29-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w215451416-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP306-500_JPN-w215451416-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP34-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP34-500_JPN-JP36-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w66098469-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP36-500_JPN-w66098469-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP41-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP37-500_JPN-JP41-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP4-275_JPN</t>
+  </si>
+  <si>
+    <t>g_JP4-275_JPN-JP2-275_JPN</t>
+  </si>
+  <si>
+    <t>g_JP4-275_JPN-JP5-275_JPN</t>
+  </si>
+  <si>
+    <t>e_w168857610-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP41-500_JPN-w168857610-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP49-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP50-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP49-500_JPN-JP50-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP5-275_JPN-JP2-275_JPN</t>
+  </si>
+  <si>
+    <t>e_JP6-275_JPN</t>
+  </si>
+  <si>
+    <t>g_JP5-275_JPN-JP6-275_JPN</t>
+  </si>
+  <si>
+    <t>e_w801582512-275_JPN</t>
+  </si>
+  <si>
+    <t>g_JP5-275_JPN-w801582512-275_JPN</t>
+  </si>
+  <si>
+    <t>e_w133641619-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP50-500_JPN-w133641619-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP57-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w169249243-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP57-500_JPN-w169249243-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP6-275_JPN-JP5-275_JPN</t>
+  </si>
+  <si>
+    <t>e_JP7-275_JPN</t>
+  </si>
+  <si>
+    <t>g_JP6-275_JPN-JP7-275_JPN</t>
+  </si>
+  <si>
+    <t>e_JP60-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w104530060-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP60-500_JPN-w104530060-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP7-275_JPN-JP6-275_JPN</t>
+  </si>
+  <si>
+    <t>e_JP74-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP74-500_JPN-JP57-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP76-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP73-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP76-500_JPN-JP73-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP9-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w1028554758-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP9-500_JPN-w1028554758-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP95-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w150035494-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP95-500_JPN-w150035494-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w832823487-500_JPN</t>
+  </si>
+  <si>
+    <t>g_JP96-500_JPN-w832823487-500_JPN</t>
+  </si>
+  <si>
+    <t>g_r11529219-500_JPN-JP118-500_JPN</t>
+  </si>
+  <si>
+    <t>g_r11529637-500_JPN-JP124-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP155-500_JPN</t>
+  </si>
+  <si>
+    <t>g_r11529637-500_JPN-JP155-500_JPN</t>
+  </si>
+  <si>
+    <t>e_r13768299-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w168727982-500_JPN</t>
+  </si>
+  <si>
+    <t>g_r13768299-500_JPN-w168727982-500_JPN</t>
+  </si>
+  <si>
+    <t>e_r15580570-500_JPN</t>
+  </si>
+  <si>
+    <t>g_r15580570-500_JPN-r13768299-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w132913106-500_JPN</t>
+  </si>
+  <si>
+    <t>g_r15580570-500_JPN-w132913106-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w168839127-500_JPN</t>
+  </si>
+  <si>
+    <t>g_r15580570-500_JPN-w168839127-500_JPN</t>
+  </si>
+  <si>
+    <t>e_r17013811-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP25-500_JPN</t>
+  </si>
+  <si>
+    <t>g_r17013811-500_JPN-JP25-500_JPN</t>
+  </si>
+  <si>
+    <t>g_r17013811-500_JPN-w169249243-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w256682313-500_JPN</t>
+  </si>
+  <si>
+    <t>g_r17013811-500_JPN-w256682313-500_JPN</t>
+  </si>
+  <si>
+    <t>e_r2269992-500_JPN</t>
+  </si>
+  <si>
+    <t>g_r2269992-500_JPN-JP110-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w714627759-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w1028554758-500_JPN-w714627759-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w1029010255-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w1029010255-500_JPN-r11529219-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w102958903-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w87538349-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w102958903-500_JPN-w87538349-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w1030329139-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w1030329139-500_JPN-JP29-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w106309481-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w104391636-500_JPN-w106309481-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w104391636-500_JPN-w132913106-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w104391636-500_JPN-w168839127-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w104530060-500_JPN-w168839127-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w104173570-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w106309481-500_JPN-w104173570-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w109834508-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w109850439-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w109834508-500_JPN-w109850439-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w169031998-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w109850439-500_JPN-w169031998-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w291678103-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w109850439-500_JPN-w291678103-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w110682956-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w110682956-500_JPN-JP158-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w105298089-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w132913106-500_JPN-w105298089-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w133641619-500_JPN-r15580570-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w128581912-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w133641619-500_JPN-w128581912-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w133644487-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w133641619-500_JPN-w133644487-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w145079972-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w133644487-500_JPN-w145079972-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w142662111-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w116559939-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w142662111-500_JPN-w116559939-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w170850727-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w142662111-500_JPN-w170850727-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w209429410-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w142662111-500_JPN-w209429410-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w142662111-500_JPN-w459476442-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w149843487-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w145079972-500_JPN-w149843487-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w150065045-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w150035494-500_JPN-w150065045-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w150065045-500_JPN-w149843487-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w151379730-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w151379730-500_JPN-w168727982-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w156208858-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w156208858-500_JPN-JP19-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w253566674-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w156208858-500_JPN-w253566674-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w161727149-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w161727149-500_JPN-JP191-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w161870227-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w161727149-500_JPN-w161870227-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w169359724-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w161727149-500_JPN-w169359724-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w161870227-500_JPN-w169031998-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w161870227-500_JPN-w170589736-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w168727982-500_JPN-JP101-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w168727982-500_JPN-w105298089-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w168857610-500_JPN-w104391636-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w168857610-500_JPN-w104530060-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w169031921-500_JPN-w161727149-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w320438391-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w169031921-500_JPN-w320438391-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w169031921-500_JPN-w421647841-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w1038584990-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w169031998-500_JPN-w1038584990-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w169122898-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w169122898-500_JPN-w116559939-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w161946849-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w169122898-500_JPN-w161946849-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w169359724-500_JPN-JP249-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w169359724-500_JPN-w109834508-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w169963227-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w195615141-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w169963227-500_JPN-w195615141-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w169963227-500_JPN-w66098469-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w170247312-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w170247312-500_JPN-w169122898-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w170366035-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w170366035-500_JPN-w161946849-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w170366035-500_JPN-w170850727-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w975217734-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w170366035-500_JPN-w975217734-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w170537514-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w190769051-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w170537514-500_JPN-w190769051-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w170568495-500_JPN-w170366035-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w170568495-500_JPN-w170537514-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w170605907-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w170605907-500_JPN-JP178-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w170605907-500_JPN-w110682956-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w171066843-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w171066843-500_JPN-w87538349-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w172144358-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w172144358-500_JPN-w172601929-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w201293312-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w172144358-500_JPN-w201293312-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w405626236-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w172144358-500_JPN-w405626236-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w187988970-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w172601929-500_JPN-w187988970-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w172907196-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w1037299172-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w172907196-500_JPN-w1037299172-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w172907196-500_JPN-w171066843-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w106076988-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w174636874-500_JPN-w106076988-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w179863079-275_JPN</t>
+  </si>
+  <si>
+    <t>g_w179863079-275_JPN-JP2-275_JPN</t>
+  </si>
+  <si>
+    <t>g_w179863079-275_JPN-JP6-275_JPN</t>
+  </si>
+  <si>
+    <t>g_w185029969-500_JPN-w172144358-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w186510275-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w186510275-500_JPN-JP267-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w187988970-500_JPN-w201293312-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w204258596-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w187988970-500_JPN-w204258596-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w190769051-500_JPN-JP112-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w190769051-500_JPN-w161946849-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w193544791-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w170974371-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w193544791-500_JPN-w170974371-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w317416612-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w193544791-500_JPN-w317416612-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w195615141-500_JPN-w145079972-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w201293312-500_JPN-w216778426-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w204258596-500_JPN-w317416612-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w209726348-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w209429410-500_JPN-w209726348-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w210090094-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w210090094-500_JPN-JP219-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w210090094-500_JPN-w116559939-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w211412000-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w211412000-500_JPN-w315461272-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w216956620-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w215451416-500_JPN-w216956620-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w216502300-500_JPN-w215451416-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w216502300-500_JPN-w405626236-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w216953915-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w216956620-500_JPN-w216953915-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w241822621-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w241822621-500_JPN-JP155-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w241822621-500_JPN-w320438391-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w241822623-500_JPN-w241822631-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w241822631-500_JPN-w241822621-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w241828221-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w241828221-500_JPN-w170974371-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w241828221-500_JPN-w241822623-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w242103481-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w241828221-500_JPN-w242103481-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w242253537-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w242103481-500_JPN-w242253537-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w242103532-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w242103532-500_JPN-JP218-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w242103532-500_JPN-w102958903-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w242253500-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w242253500-500_JPN-w193544791-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w242253500-500_JPN-w204258596-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w242253537-500_JPN-w241822621-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w250540807-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w505170104-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w250540807-500_JPN-w505170104-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w253566674-1000_JPN</t>
+  </si>
+  <si>
+    <t>e_w250540807-1000_JPN</t>
+  </si>
+  <si>
+    <t>g_w253566674-1000_JPN-w250540807-1000_JPN</t>
+  </si>
+  <si>
+    <t>g_w253566674-500_JPN-w104391636-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w256682313-500_JPN-w169249243-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w291678103-500_JPN-w109834508-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w307942220-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w307942220-500_JPN-w722673849-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w315434358-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w315434358-500_JPN-w195615141-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w315461272-500_JPN-w105298089-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w315618377-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w315618377-500_JPN-r11529219-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w315618377-500_JPN-w256682313-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w315662839-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w315662839-500_JPN-w195615141-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w317416612-500_JPN-w242103481-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w317511904-500_JPN-w242103481-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w320438391-500_JPN-r11529637-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w421647841-500_JPN-JP118-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w421647841-500_JPN-w110682956-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w421647841-500_JPN-w161870227-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w459476442-500_JPN-w210090094-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w505170104-500_JPN-JP60-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w505170104-500_JPN-w128581912-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w505170104-500_JPN-w315434358-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w785319805-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w659138214-500_JPN-w785319805-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w66098469-1000_JPN</t>
+  </si>
+  <si>
+    <t>e_JP28-1000_JPN</t>
+  </si>
+  <si>
+    <t>g_w66098469-1000_JPN-JP28-1000_JPN</t>
+  </si>
+  <si>
+    <t>e_w150035494-1000_JPN</t>
+  </si>
+  <si>
+    <t>g_w66098469-1000_JPN-w150035494-1000_JPN</t>
+  </si>
+  <si>
+    <t>g_w66098469-1000_JPN-w250540807-1000_JPN</t>
+  </si>
+  <si>
+    <t>g_w66098469-500_JPN-JP49-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w714627759-500_JPN-JP10-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w785319805-500_JPN-w106076988-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w801582512-275_JPN-JP5-275_JPN</t>
+  </si>
+  <si>
+    <t>e_JP8-275_JPN</t>
+  </si>
+  <si>
+    <t>g_w801582512-275_JPN-JP8-275_JPN</t>
+  </si>
+  <si>
+    <t>g_w87538349-500_JPN-w307942220-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w901872439-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w901872439-500_JPN-JP19-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w901872431-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w901872439-500_JPN-w901872431-500_JPN</t>
+  </si>
+  <si>
+    <t>g_w975217734-500_JPN-JP74-500_JPN</t>
   </si>
   <si>
     <t>~tradelinks_desc</t>
@@ -1603,7 +1606,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1658,39 +1661,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1742,7 +1745,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1853,6 +1856,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -1861,13 +1871,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1932,38 +1935,18 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FC2B5B1-43A5-4524-AA21-0E4127CB2FAB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA4D02B1-0E7C-44FD-BD84-422BDDFB7F7E}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
